--- a/帝国时代2决定版 文明联盟 弓兵流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 弓兵流最优研究顺序 By RemonBo.xlsx
@@ -1764,142 +1764,142 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>建造/工作效率提升</t>
+          <t>工作速度提升，成型更快</t>
         </is>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>玛雅</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>额外一次的投掷/发射，等于直接翻倍输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>埃塞俄比亚</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>步弓手攻击速度+18%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>攻速提升，直接抬高输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>玛雅</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>蜀</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>弩箭匣（弓兵系/战车/楼船可发更多弩箭）</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>直接强化弓兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>埃塞俄比亚</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>步弓手攻击速度+18%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>直接强化弓兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>额外一次的投掷/发射，等于直接翻倍输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>蜀</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>弩箭匣（弓兵系/战车/楼船可发更多弩箭）</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>步弓手视野 +2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>视野提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>印加</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>直接强化弓兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>蜀</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>步弓手视野 +2</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>视野提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>印加</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升</t>
+          <t>最小攻击范围缩小，贴身也能打</t>
         </is>
       </c>
     </row>
@@ -2066,9 +2066,9 @@
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -2088,14 +2088,14 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>生命值提升，抗打更久</t>
+          <t>持续回血，长期更省维修成本</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -2119,7 +2119,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="28" customHeight="1">
+    <row r="18" ht="36" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
           <t>B</t>
@@ -2142,7 +2142,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>直接强化弓兵</t>
+          <t>解锁额外单位或升级选项，本流派可用的兵种更多</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
@@ -2223,14 +2223,14 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>直接强化弓兵</t>
+          <t>提前解锁，抢一个时代的节奏</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -2250,14 +2250,14 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -2277,14 +2277,14 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -2304,14 +2304,14 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>直接强化弓兵</t>
+          <t>反弹近战伤害，换血更划算</t>
         </is>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -2336,9 +2336,9 @@
       </c>
     </row>
     <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -2363,9 +2363,9 @@
       </c>
     </row>
     <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -2385,14 +2385,14 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>直接强化弓兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>伤害提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -2412,14 +2412,14 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>直接强化弓兵</t>
+          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
         </is>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -2444,9 +2444,9 @@
       </c>
     </row>
     <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>直接强化弓兵</t>
+          <t>附加火焰伤害</t>
         </is>
       </c>
     </row>
@@ -2521,56 +2521,56 @@
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>玛雅</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>步弓手封建/城堡/帝王费用-10/20/30%</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>玛雅</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>步弓手封建/城堡/帝王费用-10/20/30%</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>蜀</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>弓兵靶场/铁匠铺科技-25%</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>蜀</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>弓兵靶场/铁匠铺科技-25%</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>直接强化弓兵</t>
         </is>
       </c>
     </row>
@@ -2597,14 +2597,14 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>资源产出/节省，加快成型</t>
+          <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>资源产出/节省，加快成型</t>
+          <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>

--- a/帝国时代2决定版 文明联盟 弓兵流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 弓兵流最优研究顺序 By RemonBo.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开局3免费位" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="后续2000金顺序" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="甲类·弓兵本体强化" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="乙类·费用与前置" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="乙类·减费用与资源效率" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="与弓兵流无关·可跳过" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主选文明推荐" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全62文明总名次" sheetId="7" state="visible" r:id="rId7"/>
@@ -18,13 +18,13 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'开局3免费位'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$30</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'后续2000金顺序'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·弓兵本体强化'!$A$1:$E$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·弓兵本体强化'!$A$1:$E$45</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'甲类·弓兵本体强化'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·费用与前置'!$A$1:$E$6</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·费用与前置'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与弓兵流无关·可跳过'!$A$1:$D$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·减费用与资源效率'!$A$1:$E$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·减费用与资源效率'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与弓兵流无关·可跳过'!$A$1:$D$31</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'与弓兵流无关·可跳过'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'主选文明推荐'!$A$1:$E$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'主选文明推荐'!$1:$1</definedName>
@@ -574,7 +574,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="51" customHeight="1">
+    <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>第 1 位</t>
@@ -587,12 +587,12 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>步弓手城堡/帝王射程+1/+2；英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）；靶场工作速度 +10%</t>
+          <t>步弓手城堡/帝王射程+1/+2；英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2 / 弱 0）；弓兵科技树 12/14；缺 扳指、帝王掷矛手；最直接一条：步弓手城堡/帝王射程+1/+2</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 0）；弓兵科技树 12/14；缺 扳指、帝王掷矛手；最直接一条：步弓手城堡/帝王射程+1/+2</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
       <c r="C3" s="4" t="inlineStr"/>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 3 条（强 2 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：弩箭匣（弓兵系/战车/楼船可发更多弩箭）</t>
+          <t>备选：阶段1·本体强化；原生条目 5 条（强 2 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：弩箭匣（弓兵系/战车/楼船可发更多弩箭）</t>
         </is>
       </c>
     </row>
@@ -620,7 +620,7 @@
       <c r="C4" s="4" t="inlineStr"/>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 1 条（强 2 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）</t>
+          <t>备选：阶段1·本体强化；原生条目 3 条（强 2 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）</t>
         </is>
       </c>
     </row>
@@ -643,16 +643,16 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>步弓手封建/城堡/帝王费用-10/20/30%；胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
+          <t>胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：步弓手封建/城堡/帝王费用-10/20/30%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：步弓手封建/城堡/帝王费用-10/20/30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="51" customHeight="1">
       <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
       <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 4 条（强 2 / 弱 2）；弓兵科技树 10/14；缺 强弩兵、扳指、护腕、帝王掷矛手；最直接一条：Malon突袭（掷石绳骑兵/投石手/掷矛手可穿透伤害）</t>
+          <t>备选：阶段1·本体强化；原生条目 6 条（强 2 / 弱 2）；弓兵科技树 10/14；缺 强弩兵、扳指、护腕、帝王掷矛手；最直接一条：Malon突袭（掷石绳骑兵/投石手/掷矛手可穿透伤害）</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       <c r="C8" s="4" t="inlineStr"/>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 2 条（强 2 / 弱 0）；弓兵科技树 12/14；缺 帝王掷矛手、环甲；最直接一条：蔷琵战士/靶场封建/城堡/帝王近战护甲+1/2/3</t>
+          <t>备选：阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；弓兵科技树 12/14；缺 帝王掷矛手、环甲；最直接一条：蔷琵战士/靶场封建/城堡/帝王近战护甲+1/2/3</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：步弓手攻击速度+18%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：步弓手攻击速度+18%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       <c r="C11" s="4" t="inlineStr"/>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 2 条（强 2 / 弱 0）；弓兵科技树 12/14；缺 扳指、帝王掷矛手；最直接一条：卡西克（蔷琵战士/投石手攻速+25%）</t>
+          <t>备选：阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；弓兵科技树 12/14；缺 扳指、帝王掷矛手；最直接一条：卡西克（蔷琵战士/投石手攻速+25%）</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       <c r="C12" s="4" t="inlineStr"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 1 条（强 1 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：掷矛手/骑象弓兵攻速+25%</t>
+          <t>备选：阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：掷矛手/骑象弓兵攻速+25%</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -813,7 +813,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>弓兵靶场/铁匠铺科技-25%；弩箭匣（弓兵系/战车/楼船可发更多弩箭）；步弓手视野 +2</t>
+          <t>弩箭匣（弓兵系/战车/楼船可发更多弩箭）；步弓手视野 +2；弓兵靶场/铁匠铺科技-25%</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -823,11 +823,11 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：弩箭匣（弓兵系/战车/楼船可发更多弩箭）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：弩箭匣（弓兵系/战车/楼船可发更多弩箭）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="51" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>5</v>
       </c>
@@ -843,7 +843,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）</t>
+          <t>安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）；织物盾（印加枪兵长/投石手/蔷琵战士近战护甲+1/远程护甲+1）</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 2 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 2 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Malon突袭（掷石绳骑兵/投石手/掷矛手可穿透伤害）；长矛兵系和掷矛手视野 +2</t>
+          <t>Malon突袭（掷石绳骑兵/投石手/掷矛手可穿透伤害）；长矛兵系和掷矛手视野 +2；聚落可训长矛/掷矛</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 2 / 弱 2）；弓兵科技树 10/14；缺 强弩兵、扳指、护腕、帝王掷矛手；最直接一条：Malon突袭（掷石绳骑兵/投石手/掷矛手可穿透伤害）</t>
+          <t>阶段1·本体强化；原生条目 6 条（强 2 / 弱 2）；弓兵科技树 10/14；缺 强弩兵、扳指、护腕、帝王掷矛手；最直接一条：Malon突袭（掷石绳骑兵/投石手/掷矛手可穿透伤害）</t>
         </is>
       </c>
     </row>
@@ -913,11 +913,11 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；弓兵科技树 12/14；缺 帝王掷矛手、环甲；最直接一条：蔷琵战士/靶场封建/城堡/帝王近战护甲+1/2/3</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；弓兵科技树 12/14；缺 帝王掷矛手、环甲；最直接一条：蔷琵战士/靶场封建/城堡/帝王近战护甲+1/2/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="51" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>8</v>
       </c>
@@ -933,7 +933,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>靶场/兵营升级食物-50%；箭毒（步弓手/防御工事造成中毒伤害）</t>
+          <t>卡西克（蔷琵战士/投石手攻速+25%）；箭毒（步弓手/防御工事造成中毒伤害）；靶场/兵营升级食物-50%</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；弓兵科技树 12/14；缺 扳指、帝王掷矛手；最直接一条：卡西克（蔷琵战士/投石手攻速+25%）</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；弓兵科技树 12/14；缺 扳指、帝王掷矛手；最直接一条：卡西克（蔷琵战士/投石手攻速+25%）</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：掷矛手/骑象弓兵攻速+25%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：掷矛手/骑象弓兵攻速+25%</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>精锐掷矛手升级免费；市政/古典掷矛手每分钟回5/10生命；轻装盾兵（掷矛手造成穿透伤害）</t>
+          <t>市政/古典掷矛手每分钟回5/10生命；轻装盾兵（掷矛手造成穿透伤害）</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 3 / 弱 0）；弓兵科技树 7/14；缺 强弩兵、弩手、弓兵、扳指；最直接一条：精锐掷矛手升级免费</t>
+          <t>阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；弓兵科技树 7/14；缺 强弩兵、弩手、弓兵、扳指；最直接一条：精锐掷矛手升级免费</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>在帝王时代可升级为帝王掷矛手</t>
+          <t>在帝王时代可升级为帝王掷矛手；步弓/掷矛生命+20%</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 1）；弓兵科技树 14/14（无缺项）；最直接一条：在帝王时代可升级为帝王掷矛手</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；弓兵科技树 14/14（无缺项）；最直接一条：在帝王时代可升级为帝王掷矛手</t>
         </is>
       </c>
     </row>
@@ -1063,17 +1063,17 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 0 / 弱 2）；弓兵科技树 12/14；缺 强弩兵、帝王掷矛手</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 2）；弓兵科技树 12/14；缺 强弩兵、帝王掷矛手</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>拜占庭</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>弓兵护甲/塔升级免费（升级炮塔需要化学）</t>
+          <t>骆驼/掷矛/长矛兵费用-25%</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1093,17 +1093,17 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；弓兵科技树 13/14；缺 帝王掷矛手</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 13/14；缺 帝王掷矛手</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="51" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>14</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>拜占庭</t>
+          <t>法兰克</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>骆驼/掷矛/长矛兵费用-25%</t>
+          <t>王家敕令骑兵（骑马弩手黄金-40%）</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；弓兵科技树 13/14；缺 帝王掷矛手</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 9/14；缺 强弩兵、扳指、护腕、帝王掷矛手；最直接一条：王家敕令骑兵（骑马弩手黄金-40%）</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
+          <t>孟加拉</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>王家敕令骑兵（骑马弩手黄金-40%）</t>
+          <t>骑兵对掷矛手攻+2</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；弓兵科技树 9/14；缺 强弩兵、扳指、护腕、帝王掷矛手；最直接一条：王家敕令骑兵（骑马弩手黄金-40%）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 12/14；缺 扳指、帝王掷矛手；最直接一条：骑兵对掷矛手攻+2</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>维京</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>骑兵对掷矛手攻+2</t>
+          <t>博格斯维加尔（弓兵系/维京长船攻+1）</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；弓兵科技树 12/14；缺 扳指、帝王掷矛手；最直接一条：骑兵对掷矛手攻+2</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 12/14；缺 扳指、帝王掷矛手；最直接一条：博格斯维加尔（弓兵系/维京长船攻+1）</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>维京</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>博格斯维加尔（弓兵系/维京长船攻+1）</t>
+          <t>兵营/靶场/马厩可用招募训令</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；弓兵科技树 12/14；缺 扳指、帝王掷矛手；最直接一条：博格斯维加尔（弓兵系/维京长船攻+1）</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；弓兵科技树 6/14；缺 强弩兵、弩手、弓兵、护腕</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>马其顿人</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>兵营/靶场/马厩可用招募训令</t>
+          <t>步弓/意大利佣兵近战护甲+1/远程护甲+1</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1243,17 +1243,17 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；弓兵科技树 6/14；缺 强弩兵、弩手、弓兵、护腕</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 13/14；缺 帝王掷矛手</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>步弓/意大利佣兵近战护甲+1/远程护甲+1</t>
+          <t>骑射手对远程攻+2（掷矛手除外）</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；弓兵科技树 13/14；缺 帝王掷矛手</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：骑射手对远程攻+2（掷矛手除外）</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>骑射手对远程攻+2（掷矛手除外）</t>
+          <t>步弓手和掷矛手对建筑的攻击力 +2</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：骑射手对远程攻+2（掷矛手除外）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：步弓手和掷矛手对建筑的攻击力 +2</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>契丹</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>步弓手和掷矛手对建筑的攻击力 +2</t>
+          <t>札甲（步兵/掷矛手反弹25%近战伤害）；掷矛/长矛/斥候骑兵系训练升级+15%</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：步弓手和掷矛手对建筑的攻击力 +2</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；弓兵科技树 12/14；缺 强弩兵、帝王掷矛手；最直接一条：札甲（步兵/掷矛手反弹25%近战伤害）</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>契丹</t>
+          <t>阿兹特克</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>札甲（步兵/掷矛手反弹25%近战伤害）</t>
+          <t>掷矛器（掷矛手攻+1，射程+1）</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -1363,17 +1363,17 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 1）；弓兵科技树 12/14；缺 强弩兵、帝王掷矛手；最直接一条：札甲（步兵/掷矛手反弹25%近战伤害）</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 11/14；缺 扳指、帝王掷矛手、环甲；最直接一条：掷矛器（掷矛手攻+1，射程+1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="51" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>23</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>阿兹特克</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>掷矛器（掷矛手攻+1，射程+1）</t>
+          <t>波斯步弓手（弓兵系消耗额外木材而非黄金）</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；弓兵科技树 11/14；缺 扳指、帝王掷矛手、环甲；最直接一条：掷矛器（掷矛手攻+1，射程+1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 11/14；缺 强弩兵、护腕、帝王掷矛手；最直接一条：波斯步弓手（弓兵系消耗额外木材而非黄金）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="51" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>24</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>普鲁人</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>波斯步弓手（弓兵系消耗额外木材而非黄金）</t>
+          <t>叶头箭杆（帕提尤达长弓兵提升近距伤害）</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；弓兵科技树 11/14；缺 强弩兵、护腕、帝王掷矛手；最直接一条：波斯步弓手（弓兵系消耗额外木材而非黄金）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 7/14；缺 强弩兵、弩手、弓兵、扳指；最直接一条：叶头箭杆（帕提尤达长弓兵提升近距伤害）</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>普鲁人</t>
+          <t>柏柏尔</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1443,27 +1443,27 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>叶头箭杆（帕提尤达长弓兵提升近距伤害）</t>
+          <t>从城堡时代开始，靶场提供标枪骑兵</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>城堡时代起</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；弓兵科技树 7/14；缺 强弩兵、弩手、弓兵、扳指；最直接一条：叶头箭杆（帕提尤达长弓兵提升近距伤害）</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；弓兵科技树 12/14；缺 强弩兵、帝王掷矛手</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>26</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>从城堡时代开始，靶场提供标枪骑兵</t>
+          <t>靶场/马厩木材-75</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；弓兵科技树 12/14；缺 强弩兵、帝王掷矛手</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；弓兵科技树 11/14；缺 强弩兵、护腕、帝王掷矛手</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>吴</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>靶场/马厩木材-75</t>
+          <t>赤壁战术（爆破船/火焰弓箭手对船只/建筑火焰伤害）</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；弓兵科技树 11/14；缺 强弩兵、护腕、帝王掷矛手</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；弓兵科技树 11/14；缺 扳指、帝王掷矛手、环甲</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>吴</t>
+          <t>瞿折罗</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>赤壁战术（爆破船/火焰弓箭手对船只/建筑火焰伤害）</t>
+          <t>边防部队（骆驼/骑象弓兵近战护甲+4）</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；弓兵科技树 11/14；缺 扳指、帝王掷矛手、环甲</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 11/14；缺 强弩兵、帝王掷矛手、环甲</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>瞿折罗</t>
+          <t>阿契美尼德</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>边防部队（骆驼/骑象弓兵近战护甲+4）</t>
+          <t>芦苇箭（弓兵/远程长生军/箭船攻速+25%）</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；弓兵科技树 11/14；缺 强弩兵、帝王掷矛手、环甲</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 9/14；缺 强弩兵、弹道学、帝王掷矛手、化学</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>阿契美尼德</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>芦苇箭（弓兵/远程长生军/箭船攻速+25%）</t>
+          <t>希洛人征兵（长矛/掷矛/村民训练+50%）</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；弓兵科技树 9/14；缺 强弩兵、弹道学、帝王掷矛手、化学</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 9/14；缺 强弩兵、弹道学、帝王掷矛手、化学</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>斯巴达</t>
+          <t>高丽</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>希洛人征兵（长矛/掷矛/村民训练+50%）</t>
+          <t>弓兵护甲/塔升级免费（升级炮塔需要化学）</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -1633,12 +1633,42 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；弓兵科技树 9/14；缺 强弩兵、弹道学、帝王掷矛手、化学</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 13/14；缺 帝王掷矛手</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>葡萄牙</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>所有单位黄金费用-20%</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>无条件</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 13/14；缺 帝王掷矛手</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F29"/>
+  <autoFilter ref="A1:F30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -1650,7 +1680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1749,22 +1779,22 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>不列颠</t>
+          <t>玛雅</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>靶场工作速度 +10%</t>
+          <t>胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>工作速度提升，成型更快</t>
+          <t>额外一次的投掷/发射，等于直接翻倍输出</t>
         </is>
       </c>
     </row>
@@ -1776,49 +1806,49 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>玛雅</t>
+          <t>埃塞俄比亚</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
+          <t>步弓手攻击速度+18%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>攻速提升，直接抬高输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>蜀</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>弩箭匣（弓兵系/战车/楼船可发更多弩箭）</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>额外一次的投掷/发射，等于直接翻倍输出</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>埃塞俄比亚</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>步弓手攻击速度+18%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>攻速提升，直接抬高输出</t>
         </is>
       </c>
     </row>
@@ -1835,17 +1865,17 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>弩箭匣（弓兵系/战车/楼船可发更多弩箭）</t>
+          <t>步弓手视野 +2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>团队加成</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>额外一次的投掷/发射，等于直接翻倍输出</t>
+          <t>视野提升</t>
         </is>
       </c>
     </row>
@@ -1862,17 +1892,17 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>步弓手视野 +2</t>
+          <t>弓兵靶场/铁匠铺科技-25%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>视野提升</t>
+          <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
@@ -1911,12 +1941,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>马普切</t>
+          <t>印加</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Malon突袭（掷石绳骑兵/投石手/掷矛手可穿透伤害）</t>
+          <t>织物盾（印加枪兵长/投石手/蔷琵战士近战护甲+1/远程护甲+1）</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1926,7 +1956,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>穿透伤害，对高护甲目标有效</t>
+          <t>护甲提升，减伤更耐打</t>
         </is>
       </c>
     </row>
@@ -1943,17 +1973,17 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>长矛兵系和掷矛手视野 +2</t>
+          <t>Malon突袭（掷石绳骑兵/投石手/掷矛手可穿透伤害）</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>视野提升</t>
+          <t>穿透伤害，对高护甲目标有效</t>
         </is>
       </c>
     </row>
@@ -1965,49 +1995,49 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>穆伊斯卡</t>
+          <t>马普切</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>蔷琵战士/靶场封建/城堡/帝王近战护甲+1/2/3</t>
+          <t>长矛兵系和掷矛手视野 +2</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>视野提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>马普切</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>聚落可训长矛/掷矛</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>护甲提升，减伤更耐打</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>穆伊斯卡</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>草药医学（弓兵系/蔷琵战士移速+15%）</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>机动性提升</t>
+          <t>解锁额外单位或升级选项，本流派可用的兵种更多</t>
         </is>
       </c>
     </row>
@@ -2019,157 +2049,157 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
+          <t>马普切</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>步兵/投石手/掷矛封建/城堡/帝王生命+5/10/15</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>生命值提升，抗打更久</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>穆伊斯卡</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>蔷琵战士/靶场封建/城堡/帝王近战护甲+1/2/3</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>穆伊斯卡</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>草药医学（弓兵系/蔷琵战士移速+15%）</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>机动性提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>图皮</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>卡西克（蔷琵战士/投石手攻速+25%）</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>攻速提升，直接抬高输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>图皮</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>箭毒（步弓手/防御工事造成中毒伤害）</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>附加中毒伤害</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>达罗毗荼</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>掷矛手/骑象弓兵攻速+25%</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>图皮</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>靶场/兵营升级食物-50%</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>攻速提升，直接抬高输出</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>色雷斯人</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>市政/古典掷矛手每分钟回5/10生命</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>持续回血，长期更省维修成本</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>色雷斯人</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>轻装盾兵（掷矛手造成穿透伤害）</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>穿透伤害，对高护甲目标有效</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="36" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>越南</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>在帝王时代可升级为帝王掷矛手</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>解锁额外单位或升级选项，本流派可用的兵种更多</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>孟加拉</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>骑兵对掷矛手攻+2</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升，正面更硬</t>
+          <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
@@ -2181,22 +2211,22 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>维京</t>
+          <t>达罗毗荼</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>博格斯维加尔（弓兵系/维京长船攻+1）</t>
+          <t>掷矛手/骑象弓兵攻速+25%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升，正面更硬</t>
+          <t>攻速提升，直接抬高输出</t>
         </is>
       </c>
     </row>
@@ -2208,270 +2238,675 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
+          <t>色雷斯人</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>市政/古典掷矛手每分钟回5/10生命</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>持续回血，长期更省维修成本</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>色雷斯人</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>轻装盾兵（掷矛手造成穿透伤害）</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>穿透伤害，对高护甲目标有效</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>越南</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>在帝王时代可升级为帝王掷矛手</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>解锁额外单位或升级选项，本流派可用的兵种更多</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>越南</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>步弓/掷矛生命+20%</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>生命值提升，抗打更久</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>立陶宛</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>长矛/掷矛移速+10%</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>机动性提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>立陶宛</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>塔盾（长矛/掷矛远程护甲+2）</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>拜占庭</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>骆驼/掷矛/长矛兵费用-25%</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>法兰克</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>王家敕令骑兵（骑马弩手黄金-40%）</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>孟加拉</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>骑兵对掷矛手攻+2</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>维京</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>博格斯维加尔（弓兵系/维京长船攻+1）</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>马其顿人</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>兵营/靶场/马厩可用招募训令</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>提前解锁，抢一个时代的节奏</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>意大利</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>步弓/意大利佣兵近战护甲+1/远程护甲+1</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>日本</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>骑射手对远程攻+2（掷矛手除外）</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>萨拉森</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>步弓手和掷矛手对建筑的攻击力 +2</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>团队加成</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>契丹</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>札甲（步兵/掷矛手反弹25%近战伤害）</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>反弹近战伤害，换血更划算</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>契丹</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>掷矛/长矛/斥候骑兵系训练升级+15%</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>训练速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>阿兹特克</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>掷矛器（掷矛手攻+1，射程+1）</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>射程提升</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>波斯</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>波斯步弓手（弓兵系消耗额外木材而非黄金）</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>资源产出/节省，加快成型</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>普鲁人</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>叶头箭杆（帕提尤达长弓兵提升近距伤害）</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>伤害提升，正面更硬</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="36" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
+    <row r="40" ht="36" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>柏柏尔</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>从城堡时代开始，靶场提供标枪骑兵</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>团队加成</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E40" s="4" t="inlineStr">
         <is>
           <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>库曼</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>靶场/马厩木材-75</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>资源产出/节省，加快成型</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>吴</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>赤壁战术（爆破船/火焰弓箭手对船只/建筑火焰伤害）</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>附加火焰伤害</t>
         </is>
       </c>
     </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>瞿折罗</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>边防部队（骆驼/骑象弓兵近战护甲+4）</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>阿契美尼德</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>芦苇箭（弓兵/远程长生军/箭船攻速+25%）</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>攻速提升，直接抬高输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>斯巴达</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>希洛人征兵（长矛/掷矛/村民训练+50%）</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>训练速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E30"/>
+  <autoFilter ref="A1:E45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -2528,125 +2963,125 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>不列颠</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>靶场工作速度 +10%</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>工作速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>玛雅</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>步弓手封建/城堡/帝王费用-10/20/30%</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>蜀</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>弓兵靶场/铁匠铺科技-25%</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>色雷斯人</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>精锐掷矛手升级免费</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>图皮</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>靶场/兵营升级食物-50%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>高丽</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>弓兵护甲/塔升级免费（升级炮塔需要化学）</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>色雷斯人</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>精锐掷矛手升级免费</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>葡萄牙</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>所有单位黄金费用-20%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>法兰克</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>王家敕令骑兵（骑马弩手黄金-40%）</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -2668,7 +3103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3076,12 +3511,12 @@
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>撒克逊人</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>海军和火药文明</t>
+          <t>步兵和防御文明</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -3091,19 +3526,19 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>海军和火药文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「采果工产食+木材」）</t>
+          <t>步兵和防御文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「磨坊/木料/采矿场建成后食物+35，石料+10」）</t>
         </is>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>撒克逊人</t>
+          <t>斯拉夫</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>步兵和防御文明</t>
+          <t>步兵和攻城文明</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -3113,19 +3548,19 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>步兵和防御文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「磨坊/木料/采矿场建成后食物+35，石料+10」）</t>
+          <t>步兵和攻城文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「农民工作速度+15%」）</t>
         </is>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>斯拉夫</t>
+          <t>条顿</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>步兵和攻城文明</t>
+          <t>步兵和防御文明</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -3135,19 +3570,19 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「农民工作速度+15%」）</t>
+          <t>步兵和防御文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「农田费用-40%」）</t>
         </is>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>条顿</t>
+          <t>土耳其</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>步兵和防御文明</t>
+          <t>火药文明</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -3157,19 +3592,19 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>步兵和防御文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「农田费用-40%」）</t>
+          <t>火药文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「金矿工速度+25%」）</t>
         </is>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>火药文明</t>
+          <t>骑兵和海军文明</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -3179,19 +3614,19 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>火药文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「金矿工速度+25%」）</t>
+          <t>骑兵和海军文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「牧羊/捕鱼/狩猎也产黄金」）</t>
         </is>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>魏</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>骑兵和海军文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -3201,19 +3636,19 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>骑兵和海军文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「牧羊/捕鱼/狩猎也产黄金」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「每研究一次经济升级免费获一村民」）</t>
         </is>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>火药和僧侣文明</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -3223,19 +3658,19 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「每研究一次经济升级免费获一村民」）</t>
+          <t>火药和僧侣文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「建筑工速度+30%」）</t>
         </is>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>西西里</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>火药和僧侣文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -3245,19 +3680,19 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>火药和僧侣文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「建筑工速度+30%」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「初始石料+100」）</t>
         </is>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
+          <t>匈奴</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -3267,19 +3702,19 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「初始石料+100」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「不需要房屋，但初始木材-100」）</t>
         </is>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>匈奴</t>
+          <t>亚美尼亚</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -3289,19 +3724,19 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「不需要房屋，但初始木材-100」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「骡车费用-25%」）</t>
         </is>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>亚美尼亚</t>
+          <t>印度斯坦</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>步兵和海军文明</t>
+          <t>骆驼和火药文明</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -3311,19 +3746,19 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「骡车费用-25%」）</t>
+          <t>骆驼和火药文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「村民黑暗/封建/城堡/帝王费用-8/13/18/23%」）</t>
         </is>
       </c>
     </row>
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>印度斯坦</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>骆驼和火药文明</t>
+          <t>步弓手和火药文明</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -3333,19 +3768,19 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>骆驼和火药文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「村民黑暗/封建/城堡/帝王费用-8/13/18/23%」）</t>
+          <t>步弓手和火药文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「初始村民+3，木材-50，食物-200」）</t>
         </is>
       </c>
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>雅典</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>步弓手和火药文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -3355,34 +3790,12 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>步弓手和火药文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「初始村民+3，木材-50，食物-200」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="36" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>雅典</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>步兵和海军文明</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>无一条直接加强弓兵</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
           <t>步兵和海军文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「TC可切换政策风格（经济/海军/军事）」）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D32"/>
+  <autoFilter ref="A1:D31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -3737,7 +4150,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>拜占庭</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -3747,7 +4160,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>弓兵护甲/塔升级免费（升级炮塔需要化学）</t>
+          <t>骆驼/掷矛/长矛兵费用-25%</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -3756,53 +4169,53 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1">
+    <row r="15" ht="36" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>拜占庭</t>
+          <t>法兰克</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>骆驼/掷矛/长矛兵费用-25%</t>
+          <t>王家敕令骑兵（骑马弩手黄金-40%）</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0）；弓兵科技树 13/14。缺：帝王掷矛手</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="36" customHeight="1">
+          <t>原生条目 1 条（强 1）；弓兵科技树 9/14。缺：强弩兵、扳指、护腕、帝王掷矛手、环甲</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
+          <t>孟加拉</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>王家敕令骑兵（骑马弩手黄金-40%）</t>
+          <t>骑兵对掷矛手攻+2</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；弓兵科技树 9/14。缺：强弩兵、扳指、护腕、帝王掷矛手、环甲</t>
+          <t>原生条目 1 条（强 1）；弓兵科技树 12/14。缺：扳指、帝王掷矛手</t>
         </is>
       </c>
     </row>
@@ -3862,7 +4275,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="51" customHeight="1">
+    <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -3883,12 +4296,12 @@
       </c>
       <c r="E2" s="10" t="inlineStr">
         <is>
-          <t>步弓手城堡/帝王射程+1/+2；英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）；靶场工作速度 +10%</t>
+          <t>步弓手城堡/帝王射程+1/+2；英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2 / 弱 0）；弓兵科技树 12/14；缺 扳指、帝王掷矛手；最直接一条：步弓手城堡/帝王射程+1/+2</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 0）；弓兵科技树 12/14；缺 扳指、帝王掷矛手；最直接一条：步弓手城堡/帝王射程+1/+2</t>
         </is>
       </c>
     </row>
@@ -3913,12 +4326,12 @@
       </c>
       <c r="E3" s="10" t="inlineStr">
         <is>
-          <t>步弓手封建/城堡/帝王费用-10/20/30%；胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
+          <t>胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：步弓手封建/城堡/帝王费用-10/20/30%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：步弓手封建/城堡/帝王费用-10/20/30%</t>
         </is>
       </c>
     </row>
@@ -3948,7 +4361,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：步弓手攻击速度+18%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：步弓手攻击速度+18%</t>
         </is>
       </c>
     </row>
@@ -3973,16 +4386,16 @@
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
-          <t>弓兵靶场/铁匠铺科技-25%；弩箭匣（弓兵系/战车/楼船可发更多弩箭）；步弓手视野 +2</t>
+          <t>弩箭匣（弓兵系/战车/楼船可发更多弩箭）；步弓手视野 +2；弓兵靶场/铁匠铺科技-25%</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：弩箭匣（弓兵系/战车/楼船可发更多弩箭）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：弩箭匣（弓兵系/战车/楼船可发更多弩箭）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="51" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -4003,12 +4416,12 @@
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）</t>
+          <t>安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）；织物盾（印加枪兵长/投石手/蔷琵战士近战护甲+1/远程护甲+1）</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 2 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 2 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）</t>
         </is>
       </c>
     </row>
@@ -4033,12 +4446,12 @@
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>Malon突袭（掷石绳骑兵/投石手/掷矛手可穿透伤害）；长矛兵系和掷矛手视野 +2</t>
+          <t>Malon突袭（掷石绳骑兵/投石手/掷矛手可穿透伤害）；长矛兵系和掷矛手视野 +2；聚落可训长矛/掷矛</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 2 / 弱 2）；弓兵科技树 10/14；缺 强弩兵、扳指、护腕、帝王掷矛手；最直接一条：Malon突袭（掷石绳骑兵/投石手/掷矛手可穿透伤害）</t>
+          <t>阶段1·本体强化；原生条目 6 条（强 2 / 弱 2）；弓兵科技树 10/14；缺 强弩兵、扳指、护腕、帝王掷矛手；最直接一条：Malon突袭（掷石绳骑兵/投石手/掷矛手可穿透伤害）</t>
         </is>
       </c>
     </row>
@@ -4068,11 +4481,11 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；弓兵科技树 12/14；缺 帝王掷矛手、环甲；最直接一条：蔷琵战士/靶场封建/城堡/帝王近战护甲+1/2/3</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；弓兵科技树 12/14；缺 帝王掷矛手、环甲；最直接一条：蔷琵战士/靶场封建/城堡/帝王近战护甲+1/2/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="51" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
@@ -4093,12 +4506,12 @@
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>靶场/兵营升级食物-50%；箭毒（步弓手/防御工事造成中毒伤害）</t>
+          <t>卡西克（蔷琵战士/投石手攻速+25%）；箭毒（步弓手/防御工事造成中毒伤害）；靶场/兵营升级食物-50%</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；弓兵科技树 12/14；缺 扳指、帝王掷矛手；最直接一条：卡西克（蔷琵战士/投石手攻速+25%）</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；弓兵科技树 12/14；缺 扳指、帝王掷矛手；最直接一条：卡西克（蔷琵战士/投石手攻速+25%）</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4541,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：掷矛手/骑象弓兵攻速+25%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：掷矛手/骑象弓兵攻速+25%</t>
         </is>
       </c>
     </row>
@@ -4153,12 +4566,12 @@
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>精锐掷矛手升级免费；市政/古典掷矛手每分钟回5/10生命；轻装盾兵（掷矛手造成穿透伤害）</t>
+          <t>市政/古典掷矛手每分钟回5/10生命；轻装盾兵（掷矛手造成穿透伤害）</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 3 / 弱 0）；弓兵科技树 7/14；缺 强弩兵、弩手、弓兵、扳指；最直接一条：精锐掷矛手升级免费</t>
+          <t>阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；弓兵科技树 7/14；缺 强弩兵、弩手、弓兵、扳指；最直接一条：精锐掷矛手升级免费</t>
         </is>
       </c>
     </row>
@@ -4183,12 +4596,12 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>在帝王时代可升级为帝王掷矛手</t>
+          <t>在帝王时代可升级为帝王掷矛手；步弓/掷矛生命+20%</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 1）；弓兵科技树 14/14（无缺项）；最直接一条：在帝王时代可升级为帝王掷矛手</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；弓兵科技树 14/14（无缺项）；最直接一条：在帝王时代可升级为帝王掷矛手</t>
         </is>
       </c>
     </row>
@@ -4218,17 +4631,17 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 0 / 弱 2）；弓兵科技树 12/14；缺 强弩兵、帝王掷矛手</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 2）；弓兵科技树 12/14；缺 强弩兵、帝王掷矛手</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>拜占庭</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -4243,22 +4656,22 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>弓兵护甲/塔升级免费（升级炮塔需要化学）</t>
+          <t>骆驼/掷矛/长矛兵费用-25%</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；弓兵科技树 13/14；缺 帝王掷矛手</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 13/14；缺 帝王掷矛手</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="51" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>拜占庭</t>
+          <t>法兰克</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -4273,12 +4686,12 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>骆驼/掷矛/长矛兵费用-25%</t>
+          <t>王家敕令骑兵（骑马弩手黄金-40%）</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；弓兵科技树 13/14；缺 帝王掷矛手</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 9/14；缺 强弩兵、扳指、护腕、帝王掷矛手；最直接一条：王家敕令骑兵（骑马弩手黄金-40%）</t>
         </is>
       </c>
     </row>
@@ -4288,7 +4701,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
+          <t>孟加拉</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -4303,12 +4716,12 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>王家敕令骑兵（骑马弩手黄金-40%）</t>
+          <t>骑兵对掷矛手攻+2</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；弓兵科技树 9/14；缺 强弩兵、扳指、护腕、帝王掷矛手；最直接一条：王家敕令骑兵（骑马弩手黄金-40%）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 12/14；缺 扳指、帝王掷矛手；最直接一条：骑兵对掷矛手攻+2</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4731,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>维京</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -4333,12 +4746,12 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>骑兵对掷矛手攻+2</t>
+          <t>博格斯维加尔（弓兵系/维京长船攻+1）</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；弓兵科技树 12/14；缺 扳指、帝王掷矛手；最直接一条：骑兵对掷矛手攻+2</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 12/14；缺 扳指、帝王掷矛手；最直接一条：博格斯维加尔（弓兵系/维京长船攻+1）</t>
         </is>
       </c>
     </row>
@@ -4348,7 +4761,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>维京</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -4363,12 +4776,12 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>博格斯维加尔（弓兵系/维京长船攻+1）</t>
+          <t>兵营/靶场/马厩可用招募训令</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；弓兵科技树 12/14；缺 扳指、帝王掷矛手；最直接一条：博格斯维加尔（弓兵系/维京长船攻+1）</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；弓兵科技树 6/14；缺 强弩兵、弩手、弓兵、护腕</t>
         </is>
       </c>
     </row>
@@ -4378,7 +4791,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>马其顿人</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -4393,22 +4806,22 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>兵营/靶场/马厩可用招募训令</t>
+          <t>步弓/意大利佣兵近战护甲+1/远程护甲+1</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；弓兵科技树 6/14；缺 强弩兵、弩手、弓兵、护腕</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 13/14；缺 帝王掷矛手</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -4423,12 +4836,12 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>步弓/意大利佣兵近战护甲+1/远程护甲+1</t>
+          <t>骑射手对远程攻+2（掷矛手除外）</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；弓兵科技树 13/14；缺 帝王掷矛手</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：骑射手对远程攻+2（掷矛手除外）</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4851,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -4453,12 +4866,12 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>骑射手对远程攻+2（掷矛手除外）</t>
+          <t>步弓手和掷矛手对建筑的攻击力 +2</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：骑射手对远程攻+2（掷矛手除外）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：步弓手和掷矛手对建筑的攻击力 +2</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4881,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>契丹</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -4483,12 +4896,12 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>步弓手和掷矛手对建筑的攻击力 +2</t>
+          <t>札甲（步兵/掷矛手反弹25%近战伤害）；掷矛/长矛/斥候骑兵系训练升级+15%</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：步弓手和掷矛手对建筑的攻击力 +2</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；弓兵科技树 12/14；缺 强弩兵、帝王掷矛手；最直接一条：札甲（步兵/掷矛手反弹25%近战伤害）</t>
         </is>
       </c>
     </row>
@@ -4498,7 +4911,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>契丹</t>
+          <t>阿兹特克</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -4513,22 +4926,22 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>札甲（步兵/掷矛手反弹25%近战伤害）</t>
+          <t>掷矛器（掷矛手攻+1，射程+1）</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 1）；弓兵科技树 12/14；缺 强弩兵、帝王掷矛手；最直接一条：札甲（步兵/掷矛手反弹25%近战伤害）</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 11/14；缺 扳指、帝王掷矛手、环甲；最直接一条：掷矛器（掷矛手攻+1，射程+1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="51" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>阿兹特克</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -4543,22 +4956,22 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>掷矛器（掷矛手攻+1，射程+1）</t>
+          <t>波斯步弓手（弓兵系消耗额外木材而非黄金）</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；弓兵科技树 11/14；缺 扳指、帝王掷矛手、环甲；最直接一条：掷矛器（掷矛手攻+1，射程+1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 11/14；缺 强弩兵、护腕、帝王掷矛手；最直接一条：波斯步弓手（弓兵系消耗额外木材而非黄金）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="51" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>普鲁人</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -4573,12 +4986,12 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>波斯步弓手（弓兵系消耗额外木材而非黄金）</t>
+          <t>叶头箭杆（帕提尤达长弓兵提升近距伤害）</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；弓兵科技树 11/14；缺 强弩兵、护腕、帝王掷矛手；最直接一条：波斯步弓手（弓兵系消耗额外木材而非黄金）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 7/14；缺 强弩兵、弩手、弓兵、扳指；最直接一条：叶头箭杆（帕提尤达长弓兵提升近距伤害）</t>
         </is>
       </c>
     </row>
@@ -4588,7 +5001,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>普鲁人</t>
+          <t>柏柏尔</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -4603,22 +5016,22 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>叶头箭杆（帕提尤达长弓兵提升近距伤害）</t>
+          <t>从城堡时代开始，靶场提供标枪骑兵</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；弓兵科技树 7/14；缺 强弩兵、弩手、弓兵、扳指；最直接一条：叶头箭杆（帕提尤达长弓兵提升近距伤害）</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；弓兵科技树 12/14；缺 强弩兵、帝王掷矛手</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -4633,12 +5046,12 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>从城堡时代开始，靶场提供标枪骑兵</t>
+          <t>靶场/马厩木材-75</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；弓兵科技树 12/14；缺 强弩兵、帝王掷矛手</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；弓兵科技树 11/14；缺 强弩兵、护腕、帝王掷矛手</t>
         </is>
       </c>
     </row>
@@ -4648,7 +5061,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>吴</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -4663,12 +5076,12 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>靶场/马厩木材-75</t>
+          <t>赤壁战术（爆破船/火焰弓箭手对船只/建筑火焰伤害）</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；弓兵科技树 11/14；缺 强弩兵、护腕、帝王掷矛手</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；弓兵科技树 11/14；缺 扳指、帝王掷矛手、环甲</t>
         </is>
       </c>
     </row>
@@ -4678,7 +5091,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>吴</t>
+          <t>瞿折罗</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
@@ -4693,12 +5106,12 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>赤壁战术（爆破船/火焰弓箭手对船只/建筑火焰伤害）</t>
+          <t>边防部队（骆驼/骑象弓兵近战护甲+4）</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 0）；弓兵科技树 11/14；缺 扳指、帝王掷矛手、环甲</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 11/14；缺 强弩兵、帝王掷矛手、环甲</t>
         </is>
       </c>
     </row>
@@ -4708,7 +5121,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>瞿折罗</t>
+          <t>阿契美尼德</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
@@ -4723,12 +5136,12 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>边防部队（骆驼/骑象弓兵近战护甲+4）</t>
+          <t>芦苇箭（弓兵/远程长生军/箭船攻速+25%）</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；弓兵科技树 11/14；缺 强弩兵、帝王掷矛手、环甲</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 9/14；缺 强弩兵、弹道学、帝王掷矛手、化学</t>
         </is>
       </c>
     </row>
@@ -4738,7 +5151,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>阿契美尼德</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
@@ -4753,12 +5166,12 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>芦苇箭（弓兵/远程长生军/箭船攻速+25%）</t>
+          <t>希洛人征兵（长矛/掷矛/村民训练+50%）</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；弓兵科技树 9/14；缺 强弩兵、弹道学、帝王掷矛手、化学</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 9/14；缺 强弩兵、弹道学、帝王掷矛手、化学</t>
         </is>
       </c>
     </row>
@@ -4768,7 +5181,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>斯巴达</t>
+          <t>高丽</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -4783,12 +5196,12 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>希洛人征兵（长矛/掷矛/村民训练+50%）</t>
+          <t>弓兵护甲/塔升级免费（升级炮塔需要化学）</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；弓兵科技树 9/14；缺 强弩兵、弹道学、帝王掷矛手、化学</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 13/14；缺 帝王掷矛手</t>
         </is>
       </c>
     </row>
@@ -4798,7 +5211,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>保加利亚</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
@@ -4808,17 +5221,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>不建议</t>
+          <t>2000 金</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>无一条直接加强弓兵</t>
+          <t>所有单位黄金费用-20%</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「民兵系升级免费」）</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 13/14；缺 帝王掷矛手</t>
         </is>
       </c>
     </row>
@@ -4828,7 +5241,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>波兰</t>
+          <t>保加利亚</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
@@ -4848,7 +5261,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「大庄园替代磨坊」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「民兵系升级免费」）</t>
         </is>
       </c>
     </row>
@@ -4858,7 +5271,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>波希米亚</t>
+          <t>波兰</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
@@ -4878,7 +5291,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>火药和僧侣文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「采矿场科技免费」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「大庄园替代磨坊」）</t>
         </is>
       </c>
     </row>
@@ -4888,7 +5301,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>勃艮第</t>
+          <t>波希米亚</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
@@ -4908,7 +5321,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「可提前一个时代经济升级且食物-40%」）</t>
+          <t>火药和僧侣文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「采矿场科技免费」）</t>
         </is>
       </c>
     </row>
@@ -4918,7 +5331,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>鞑靼</t>
+          <t>勃艮第</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
@@ -4938,7 +5351,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>骑射手文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「牲畜持续时间+50%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「可提前一个时代经济升级且食物-40%」）</t>
         </is>
       </c>
     </row>
@@ -4948,7 +5361,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>丹麦人</t>
+          <t>鞑靼</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
@@ -4968,7 +5381,7 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「捕鱼船/村民存食+5%」）</t>
+          <t>骑射手文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「牲畜持续时间+50%」）</t>
         </is>
       </c>
     </row>
@@ -4978,7 +5391,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>高棉</t>
+          <t>丹麦人</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
@@ -4998,7 +5411,7 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>攻城武器和大象文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「无需建筑即可升时代/解锁建筑」）</t>
+          <t>步兵和攻城文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「捕鱼船/村民存食+5%」）</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5421,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>哥特</t>
+          <t>高棉</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
@@ -5028,7 +5441,7 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「可立即研究织布机」）</t>
+          <t>攻城武器和大象文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「无需建筑即可升时代/解锁建筑」）</t>
         </is>
       </c>
     </row>
@@ -5038,7 +5451,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>格鲁吉亚</t>
+          <t>哥特</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
@@ -5058,7 +5471,7 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>防御和骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「开局有骡车」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「可立即研究织布机」）</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5481,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>凯尔特</t>
+          <t>格鲁吉亚</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
@@ -5088,7 +5501,7 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城武器文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「伐木工速度+15%」）</t>
+          <t>防御和骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「开局有骡车」）</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5511,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
+          <t>凯尔特</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
@@ -5118,7 +5531,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「村民收集/建造/修理速度+5%」）</t>
+          <t>步兵和攻城武器文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「伐木工速度+15%」）</t>
         </is>
       </c>
     </row>
@@ -5128,7 +5541,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>罗马</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
@@ -5148,7 +5561,7 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>海军文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「升时代速度+66%」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「村民收集/建造/修理速度+5%」）</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5571,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>马里</t>
+          <t>马来</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
@@ -5178,7 +5591,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「建筑木材-15%」）</t>
+          <t>海军文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「升时代速度+66%」）</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5601,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>马扎尔</t>
+          <t>马里</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
@@ -5208,7 +5621,7 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「村民一击杀狼」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「建筑木材-15%」）</t>
         </is>
       </c>
     </row>
@@ -5218,7 +5631,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>蒙古</t>
+          <t>马扎尔</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
@@ -5238,7 +5651,7 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>骑射手文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「猎人速度+40%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「村民一击杀狼」）</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5661,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>缅甸</t>
+          <t>蒙古</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
@@ -5268,7 +5681,7 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「伐木场科技免费」）</t>
+          <t>骑射手文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「猎人速度+40%」）</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5691,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>女真</t>
+          <t>缅甸</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
@@ -5298,7 +5711,7 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>骑兵和火药文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「伐木场科技免费」）</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5721,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>女真</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
@@ -5328,7 +5741,7 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>海军和火药文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「采果工产食+木材」）</t>
+          <t>骑兵和火药文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
         </is>
       </c>
     </row>
@@ -5735,7 +6148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5866,101 +6279,141 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>① 只看直接作用于弓兵本体、或其前置/费用/产出的条目；</t>
+          <t>本表按用户打法口径分四个阶段排序：先加强要玩的主流派兵种，再减它的资源消耗，最后才补资源效率。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1">
-      <c r="A14" s="12" t="inlineStr"/>
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>① 阶段 1 · 本体强化</t>
+        </is>
+      </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>② 泛用条目与兵种类一律剔除（放进「与弓兵流无关·可跳过」）；</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="19" customHeight="1">
-      <c r="A15" s="12" t="inlineStr"/>
+          <t>直接加强弓兵本体的条目（攻击/护甲/生命/攻速/射程/移速/回血/数量/生产训练速度/解锁升级等）。这一档最优先。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>② 阶段 2 · 减费用</t>
+        </is>
+      </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>③ 门槛越低、替代成本越高，名次越靠前。</t>
+          <t>降低该兵种及同系兵种（靶场远程系（步弓/掷矛手/投石手等））生产所需资源的条目：费用/成本 -N%、升级免费、用其它资源替代。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1">
-      <c r="A16" s="12" t="inlineStr"/>
-      <c r="B16" s="12" t="inlineStr"/>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>③ 阶段 3 · 资源效率</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>采集/产出/携带/贸易/人口/经济科技等让主流派更快成型的条目。</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="19" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>未验证项</t>
+          <t>④ 阶段 4 · 其他相关</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>本表的档位与名次为依据「条目文本 + 官方科技树」的经验判断，未逐项实测；与实战不符时以实战为准。</t>
+          <t>其余与本流派相关、但不属于上述三类的条目。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>★ 最重要的一条：别买重复</t>
-        </is>
-      </c>
+      <c r="A18" s="12" t="inlineStr"/>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>主选文明已经自带的加成，不要再用按钮买一遍——一个按钮只能研究一次，重复等于白花 2000 金。</t>
+          <t>同阶段内按「人工权威顺序（实战强度）」再排；泛用条目与兵种类一律剔除（放进「与弓兵流无关·可跳过」）。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="12" t="inlineStr"/>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>正确流程是：先定主选文明（见「主选文明推荐」），再按剩下的缺口挑 3 个免费位。</t>
-        </is>
-      </c>
+      <c r="B19" s="12" t="inlineStr"/>
     </row>
     <row r="20" ht="19" customHeight="1">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>数据来源</t>
+          <t>未验证项</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>用户提供的 62 张文明卡片 PNG（By RemonBo）+ 游戏官方简体中文字串逐条核对。</t>
+          <t>本表的档位与名次为依据「条目文本 + 官方科技树」的经验判断，未逐项实测；与实战不符时以实战为准。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="12" t="inlineStr"/>
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>★ 最重要的一条：别买重复</t>
+        </is>
+      </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>主选文明的科技树数据来自游戏官方 CivTechTrees 的 62 份 JSON。</t>
+          <t>主选文明已经自带的加成，不要再用按钮买一遍——一个按钮只能研究一次，重复等于白花 2000 金。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>整理</t>
-        </is>
-      </c>
+      <c r="A22" s="12" t="inlineStr"/>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>By RemonBo；本表由 DSH 生成。</t>
+          <t>正确流程是：先定主选文明（见「主选文明推荐」），再按剩下的缺口挑 3 个免费位。</t>
         </is>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="12" t="inlineStr">
         <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>用户提供的 62 张文明卡片 PNG（By RemonBo）+ 游戏官方简体中文字串逐条核对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="19" customHeight="1">
+      <c r="A24" s="12" t="inlineStr"/>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>主选文明的科技树数据来自游戏官方 CivTechTrees 的 62 份 JSON。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>整理</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>By RemonBo；本表由 DSH 生成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="19" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
           <t>与本表配套</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>同目录下的箭塔流、炮塔流与其余流派总表。</t>
         </is>

--- a/帝国时代2决定版 文明联盟 弓兵流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 弓兵流最优研究顺序 By RemonBo.xlsx
@@ -18,13 +18,13 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'开局3免费位'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$28</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'后续2000金顺序'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·弓兵本体强化'!$A$1:$E$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·弓兵本体强化'!$A$1:$E$38</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'甲类·弓兵本体强化'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·减费用与资源效率'!$A$1:$E$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·减费用与资源效率'!$A$1:$E$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·减费用与资源效率'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与弓兵流无关·可跳过'!$A$1:$D$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与弓兵流无关·可跳过'!$A$1:$D$33</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'与弓兵流无关·可跳过'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'主选文明推荐'!$A$1:$E$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'主选文明推荐'!$1:$1</definedName>
@@ -102,12 +102,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8CBAD"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -163,11 +163,11 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -574,7 +574,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1">
+    <row r="2" ht="51" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>第 1 位</t>
@@ -587,7 +587,7 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>步弓手城堡/帝王射程+1/+2；英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
+          <t>步弓手城堡/帝王射程+1/+2；英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）；靶场工作速度 +10%</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
@@ -754,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -813,7 +813,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>弩箭匣（弓兵系/战车/楼船可发更多弩箭）；步弓手视野 +2；弓兵靶场/铁匠铺科技-25%</t>
+          <t>步弓手视野 +2；弩箭匣（弓兵系/战车/楼船可发更多弩箭）</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Malon突袭（掷石绳骑兵/投石手/掷矛手可穿透伤害）；长矛兵系和掷矛手视野 +2；聚落可训长矛/掷矛</t>
+          <t>Malon突袭（掷石绳骑兵/投石手/掷矛手可穿透伤害）；步兵/投石手/掷矛封建/城堡/帝王生命+5/10/15；长矛兵系和掷矛手视野 +2</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -917,7 +917,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="51" customHeight="1">
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>8</v>
       </c>
@@ -933,7 +933,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>卡西克（蔷琵战士/投石手攻速+25%）；箭毒（步弓手/防御工事造成中毒伤害）；靶场/兵营升级食物-50%</t>
+          <t>卡西克（蔷琵战士/投石手攻速+25%）；箭毒（步弓手/防御工事造成中毒伤害）</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>在帝王时代可升级为帝王掷矛手；步弓/掷矛生命+20%</t>
+          <t>步弓/掷矛生命+20%；在帝王时代可升级为帝王掷矛手</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>拜占庭</t>
+          <t>维京</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>骆驼/掷矛/长矛兵费用-25%</t>
+          <t>博格斯维加尔（弓兵系/维京长船攻+1）</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1093,17 +1093,17 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 13/14；缺 帝王掷矛手</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 12/14；缺 扳指、帝王掷矛手；最直接一条：博格斯维加尔（弓兵系/维京长船攻+1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>14</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>王家敕令骑兵（骑马弩手黄金-40%）</t>
+          <t>兵营/靶场/马厩可用招募训令</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 9/14；缺 强弩兵、扳指、护腕、帝王掷矛手；最直接一条：王家敕令骑兵（骑马弩手黄金-40%）</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；弓兵科技树 6/14；缺 强弩兵、弩手、弓兵、护腕</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>骑兵对掷矛手攻+2</t>
+          <t>步弓/意大利佣兵近战护甲+1/远程护甲+1</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 12/14；缺 扳指、帝王掷矛手；最直接一条：骑兵对掷矛手攻+2</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 13/14；缺 帝王掷矛手</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>维京</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>博格斯维加尔（弓兵系/维京长船攻+1）</t>
+          <t>步弓手和掷矛手对建筑的攻击力 +2</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 12/14；缺 扳指、帝王掷矛手；最直接一条：博格斯维加尔（弓兵系/维京长船攻+1）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：步弓手和掷矛手对建筑的攻击力 +2</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>马其顿人</t>
+          <t>契丹</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>兵营/靶场/马厩可用招募训令</t>
+          <t>札甲（步兵/掷矛手反弹25%近战伤害）；掷矛/长矛/斥候骑兵系训练升级+15%</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；弓兵科技树 6/14；缺 强弩兵、弩手、弓兵、护腕</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；弓兵科技树 12/14；缺 强弩兵、帝王掷矛手；最直接一条：札甲（步兵/掷矛手反弹25%近战伤害）</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>阿兹特克</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>步弓/意大利佣兵近战护甲+1/远程护甲+1</t>
+          <t>掷矛器（掷矛手攻+1，射程+1）</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 13/14；缺 帝王掷矛手</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 11/14；缺 扳指、帝王掷矛手、环甲；最直接一条：掷矛器（掷矛手攻+1，射程+1）</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>瞿折罗</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>骑射手对远程攻+2（掷矛手除外）</t>
+          <t>边防部队（骆驼/骑象弓兵近战护甲+4）</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：骑射手对远程攻+2（掷矛手除外）</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 11/14；缺 强弩兵、帝王掷矛手、环甲</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>阿契美尼德</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>步弓手和掷矛手对建筑的攻击力 +2</t>
+          <t>芦苇箭（弓兵/远程长生军/箭船攻速+25%）</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：步弓手和掷矛手对建筑的攻击力 +2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 9/14；缺 强弩兵、弹道学、帝王掷矛手、化学</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="51" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>21</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>契丹</t>
+          <t>普鲁人</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>札甲（步兵/掷矛手反弹25%近战伤害）；掷矛/长矛/斥候骑兵系训练升级+15%</t>
+          <t>叶头箭杆（帕提尤达长弓兵提升近距伤害）</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；弓兵科技树 12/14；缺 强弩兵、帝王掷矛手；最直接一条：札甲（步兵/掷矛手反弹25%近战伤害）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 7/14；缺 强弩兵、弩手、弓兵、扳指；最直接一条：叶头箭杆（帕提尤达长弓兵提升近距伤害）</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>阿兹特克</t>
+          <t>柏柏尔</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1353,27 +1353,27 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>掷矛器（掷矛手攻+1，射程+1）</t>
+          <t>从城堡时代开始，靶场提供标枪骑兵</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>城堡时代起</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 11/14；缺 扳指、帝王掷矛手、环甲；最直接一条：掷矛器（掷矛手攻+1，射程+1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；弓兵科技树 12/14；缺 强弩兵、帝王掷矛手</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>23</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>吴</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>波斯步弓手（弓兵系消耗额外木材而非黄金）</t>
+          <t>赤壁战术（爆破船/火焰弓箭手对船只/建筑火焰伤害）</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 11/14；缺 强弩兵、护腕、帝王掷矛手；最直接一条：波斯步弓手（弓兵系消耗额外木材而非黄金）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；弓兵科技树 11/14；缺 扳指、帝王掷矛手、环甲</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>24</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>普鲁人</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>叶头箭杆（帕提尤达长弓兵提升近距伤害）</t>
+          <t>希洛人征兵（长矛/掷矛/村民训练+50%）</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 7/14；缺 强弩兵、弩手、弓兵、扳指；最直接一条：叶头箭杆（帕提尤达长弓兵提升近距伤害）</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 9/14；缺 强弩兵、弹道学、帝王掷矛手、化学</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>拜占庭</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1443,27 +1443,27 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>从城堡时代开始，靶场提供标枪骑兵</t>
+          <t>骆驼/掷矛/长矛兵费用-25%</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；弓兵科技树 12/14；缺 强弩兵、帝王掷矛手</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="36" customHeight="1">
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 13/14；缺 帝王掷矛手</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="51" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>26</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>法兰克</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>靶场/马厩木材-75</t>
+          <t>王家敕令骑兵（骑马弩手黄金-40%）</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -1483,17 +1483,17 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；弓兵科技树 11/14；缺 强弩兵、护腕、帝王掷矛手</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="36" customHeight="1">
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 9/14；缺 强弩兵、扳指、护腕、帝王掷矛手；最直接一条：王家敕令骑兵（骑马弩手黄金-40%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="51" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>27</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>吴</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>赤壁战术（爆破船/火焰弓箭手对船只/建筑火焰伤害）</t>
+          <t>波斯步弓手（弓兵系消耗额外木材而非黄金）</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；弓兵科技树 11/14；缺 扳指、帝王掷矛手、环甲</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 11/14；缺 强弩兵、护腕、帝王掷矛手；最直接一条：波斯步弓手（弓兵系消耗额外木材而非黄金）</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>瞿折罗</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>边防部队（骆驼/骑象弓兵近战护甲+4）</t>
+          <t>靶场/马厩木材-75</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 11/14；缺 强弩兵、帝王掷矛手、环甲</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 0）；弓兵科技树 11/14；缺 强弩兵、护腕、帝王掷矛手</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>阿契美尼德</t>
+          <t>高丽</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>芦苇箭（弓兵/远程长生军/箭船攻速+25%）</t>
+          <t>弓兵护甲/塔升级免费（升级炮塔需要化学）</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 9/14；缺 强弩兵、弹道学、帝王掷矛手、化学</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 13/14；缺 帝王掷矛手</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>斯巴达</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>希洛人征兵（长矛/掷矛/村民训练+50%）</t>
+          <t>所有单位黄金费用-20%</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -1603,72 +1603,12 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 9/14；缺 强弩兵、弹道学、帝王掷矛手、化学</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="36" customHeight="1">
-      <c r="A29" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>高丽</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>弓兵护甲/塔升级免费（升级炮塔需要化学）</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>无条件</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
           <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 13/14；缺 帝王掷矛手</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="36" customHeight="1">
-      <c r="A30" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>葡萄牙</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>所有单位黄金费用-20%</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>无条件</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 13/14；缺 帝王掷矛手</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F30"/>
+  <autoFilter ref="A1:F28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -1680,7 +1620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1718,7 +1658,7 @@
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -1745,7 +1685,7 @@
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -1772,83 +1712,83 @@
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>不列颠</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>靶场工作速度 +10%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>工作速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>玛雅</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>额外一次的投掷/发射，等于直接翻倍输出</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>埃塞俄比亚</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>步弓手攻击速度+18%</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>攻速提升，直接抬高输出</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>蜀</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>弩箭匣（弓兵系/战车/楼船可发更多弩箭）</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>额外一次的投掷/发射，等于直接翻倍输出</t>
         </is>
       </c>
     </row>
@@ -1865,17 +1805,17 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>步弓手视野 +2</t>
+          <t>弩箭匣（弓兵系/战车/楼船可发更多弩箭）</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>视野提升</t>
+          <t>额外一次的投掷/发射，等于直接翻倍输出</t>
         </is>
       </c>
     </row>
@@ -1892,17 +1832,17 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>弓兵靶场/铁匠铺科技-25%</t>
+          <t>步弓手视野 +2</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>团队加成</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>降低费用，让该流派更快成型</t>
+          <t>视野提升</t>
         </is>
       </c>
     </row>
@@ -2177,19 +2117,19 @@
       </c>
     </row>
     <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>图皮</t>
+          <t>达罗毗荼</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>靶场/兵营升级食物-50%</t>
+          <t>掷矛手/骑象弓兵攻速+25%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2199,7 +2139,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>降低费用，让该流派更快成型</t>
+          <t>攻速提升，直接抬高输出</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2151,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>达罗毗荼</t>
+          <t>色雷斯人</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>掷矛手/骑象弓兵攻速+25%</t>
+          <t>市政/古典掷矛手每分钟回5/10生命</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -2226,7 +2166,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>攻速提升，直接抬高输出</t>
+          <t>持续回血，长期更省维修成本</t>
         </is>
       </c>
     </row>
@@ -2243,71 +2183,71 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>市政/古典掷矛手每分钟回5/10生命</t>
+          <t>轻装盾兵（掷矛手造成穿透伤害）</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>穿透伤害，对高护甲目标有效</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>越南</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>在帝王时代可升级为帝王掷矛手</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>解锁额外单位或升级选项，本流派可用的兵种更多</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>越南</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>步弓/掷矛生命+20%</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>持续回血，长期更省维修成本</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>色雷斯人</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>轻装盾兵（掷矛手造成穿透伤害）</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>穿透伤害，对高护甲目标有效</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="36" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>越南</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>在帝王时代可升级为帝王掷矛手</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>解锁额外单位或升级选项，本流派可用的兵种更多</t>
+          <t>生命值提升，抗打更久</t>
         </is>
       </c>
     </row>
@@ -2319,12 +2259,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>越南</t>
+          <t>立陶宛</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>步弓/掷矛生命+20%</t>
+          <t>长矛/掷矛移速+10%</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2334,7 +2274,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>生命值提升，抗打更久</t>
+          <t>机动性提升</t>
         </is>
       </c>
     </row>
@@ -2351,17 +2291,17 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>长矛/掷矛移速+10%</t>
+          <t>塔盾（长矛/掷矛远程护甲+2）</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>机动性提升</t>
+          <t>护甲提升，减伤更耐打</t>
         </is>
       </c>
     </row>
@@ -2373,12 +2313,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>立陶宛</t>
+          <t>维京</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>塔盾（长矛/掷矛远程护甲+2）</t>
+          <t>博格斯维加尔（弓兵系/维京长船攻+1）</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2388,7 +2328,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>护甲提升，减伤更耐打</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
@@ -2400,12 +2340,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>拜占庭</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>骆驼/掷矛/长矛兵费用-25%</t>
+          <t>兵营/靶场/马厩可用招募训令</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -2415,7 +2355,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>降低费用，让该流派更快成型</t>
+          <t>提前解锁，抢一个时代的节奏</t>
         </is>
       </c>
     </row>
@@ -2427,22 +2367,22 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>王家敕令骑兵（骑马弩手黄金-40%）</t>
+          <t>步弓/意大利佣兵近战护甲+1/远程护甲+1</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>降低费用，让该流派更快成型</t>
+          <t>护甲提升，减伤更耐打</t>
         </is>
       </c>
     </row>
@@ -2454,17 +2394,17 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>骑兵对掷矛手攻+2</t>
+          <t>步弓手和掷矛手对建筑的攻击力 +2</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>团队加成</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -2481,12 +2421,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>维京</t>
+          <t>契丹</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>博格斯维加尔（弓兵系/维京长船攻+1）</t>
+          <t>札甲（步兵/掷矛手反弹25%近战伤害）</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -2496,7 +2436,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升，正面更硬</t>
+          <t>反弹近战伤害，换血更划算</t>
         </is>
       </c>
     </row>
@@ -2508,12 +2448,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>马其顿人</t>
+          <t>契丹</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>兵营/靶场/马厩可用招募训令</t>
+          <t>掷矛/长矛/斥候骑兵系训练升级+15%</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2523,7 +2463,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>提前解锁，抢一个时代的节奏</t>
+          <t>训练速度提升，成型更快</t>
         </is>
       </c>
     </row>
@@ -2535,22 +2475,22 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>阿兹特克</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>步弓/意大利佣兵近战护甲+1/远程护甲+1</t>
+          <t>掷矛器（掷矛手攻+1，射程+1）</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>护甲提升，减伤更耐打</t>
+          <t>射程提升</t>
         </is>
       </c>
     </row>
@@ -2562,22 +2502,22 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>瞿折罗</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>骑射手对远程攻+2（掷矛手除外）</t>
+          <t>边防部队（骆驼/骑象弓兵近战护甲+4）</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升，正面更硬</t>
+          <t>护甲提升，减伤更耐打</t>
         </is>
       </c>
     </row>
@@ -2589,22 +2529,22 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>阿契美尼德</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>步弓手和掷矛手对建筑的攻击力 +2</t>
+          <t>芦苇箭（弓兵/远程长生军/箭船攻速+25%）</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升，正面更硬</t>
+          <t>攻速提升，直接抬高输出</t>
         </is>
       </c>
     </row>
@@ -2616,12 +2556,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>契丹</t>
+          <t>普鲁人</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>札甲（步兵/掷矛手反弹25%近战伤害）</t>
+          <t>叶头箭杆（帕提尤达长弓兵提升近距伤害）</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2631,11 +2571,11 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>反弹近战伤害，换血更划算</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="28" customHeight="1">
+          <t>伤害提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="36" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
           <t>C</t>
@@ -2643,22 +2583,22 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>契丹</t>
+          <t>柏柏尔</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>掷矛/长矛/斥候骑兵系训练升级+15%</t>
+          <t>从城堡时代开始，靶场提供标枪骑兵</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>团队加成</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>训练速度提升，成型更快</t>
+          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2610,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>阿兹特克</t>
+          <t>吴</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>掷矛器（掷矛手攻+1，射程+1）</t>
+          <t>赤壁战术（爆破船/火焰弓箭手对船只/建筑火焰伤害）</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2685,7 +2625,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>射程提升</t>
+          <t>附加火焰伤害</t>
         </is>
       </c>
     </row>
@@ -2697,12 +2637,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>波斯步弓手（弓兵系消耗额外木材而非黄金）</t>
+          <t>希洛人征兵（长矛/掷矛/村民训练+50%）</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2712,201 +2652,12 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>普鲁人</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>叶头箭杆（帕提尤达长弓兵提升近距伤害）</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>伤害提升，正面更硬</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="36" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>柏柏尔</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>从城堡时代开始，靶场提供标枪骑兵</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>库曼</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>靶场/马厩木材-75</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="28" customHeight="1">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>吴</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>赤壁战术（爆破船/火焰弓箭手对船只/建筑火焰伤害）</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>附加火焰伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="28" customHeight="1">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>瞿折罗</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>边防部队（骆驼/骑象弓兵近战护甲+4）</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>护甲提升，减伤更耐打</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="28" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>阿契美尼德</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>芦苇箭（弓兵/远程长生军/箭船攻速+25%）</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>攻速提升，直接抬高输出</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="28" customHeight="1">
-      <c r="A45" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>斯巴达</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>希洛人征兵（长矛/掷矛/村民训练+50%）</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
           <t>训练速度提升，成型更快</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E45"/>
+  <autoFilter ref="A1:E38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -2918,7 +2669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2956,46 +2707,46 @@
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>不列颠</t>
+          <t>玛雅</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>靶场工作速度 +10%</t>
+          <t>步弓手封建/城堡/帝王费用-10/20/30%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>工作速度提升，成型更快</t>
+          <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>玛雅</t>
+          <t>蜀</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>步弓手封建/城堡/帝王费用-10/20/30%</t>
+          <t>弓兵靶场/铁匠铺科技-25%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -3009,89 +2760,224 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>图皮</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>靶场/兵营升级食物-50%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>色雷斯人</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>精锐掷矛手升级免费</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>拜占庭</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>骆驼/掷矛/长矛兵费用-25%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>法兰克</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>王家敕令骑兵（骑马弩手黄金-40%）</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>波斯</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>波斯步弓手（弓兵系消耗额外木材而非黄金）</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>库曼</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>靶场/马厩木材-75</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>高丽</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>弓兵护甲/塔升级免费（升级炮塔需要化学）</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>葡萄牙</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>所有单位黄金费用-20%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E6"/>
+  <autoFilter ref="A1:E11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -3103,7 +2989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3467,12 +3353,12 @@
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>缅甸</t>
+          <t>孟加拉</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>象兵和海军文明</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -3482,19 +3368,19 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「伐木场科技免费」）</t>
+          <t>象兵和海军文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「升时代TC产生2村民」）</t>
         </is>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>女真</t>
+          <t>缅甸</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>骑兵和火药文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -3504,19 +3390,19 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>骑兵和火药文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「伐木场科技免费」）</t>
         </is>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>撒克逊人</t>
+          <t>女真</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>步兵和防御文明</t>
+          <t>骑兵和火药文明</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -3526,19 +3412,19 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>步兵和防御文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「磨坊/木料/采矿场建成后食物+35，石料+10」）</t>
+          <t>骑兵和火药文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
         </is>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>斯拉夫</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>步兵和攻城文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -3548,14 +3434,14 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「农民工作速度+15%」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「磨坊/伐木场/采矿场费用-50%」）</t>
         </is>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>条顿</t>
+          <t>撒克逊人</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -3570,19 +3456,19 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>步兵和防御文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「农田费用-40%」）</t>
+          <t>步兵和防御文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「磨坊/木料/采矿场建成后食物+35，石料+10」）</t>
         </is>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>斯拉夫</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>火药文明</t>
+          <t>步兵和攻城文明</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -3592,19 +3478,19 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>火药文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「金矿工速度+25%」）</t>
+          <t>步兵和攻城文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「农民工作速度+15%」）</t>
         </is>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>条顿</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>骑兵和海军文明</t>
+          <t>步兵和防御文明</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -3614,19 +3500,19 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>骑兵和海军文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「牧羊/捕鱼/狩猎也产黄金」）</t>
+          <t>步兵和防御文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「农田费用-40%」）</t>
         </is>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
+          <t>土耳其</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>火药文明</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -3636,19 +3522,19 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「每研究一次经济升级免费获一村民」）</t>
+          <t>火药文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「金矿工速度+25%」）</t>
         </is>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>火药和僧侣文明</t>
+          <t>骑兵和海军文明</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -3658,19 +3544,19 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>火药和僧侣文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「建筑工速度+30%」）</t>
+          <t>骑兵和海军文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「牧羊/捕鱼/狩猎也产黄金」）</t>
         </is>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
+          <t>魏</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -3680,19 +3566,19 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「初始石料+100」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「每研究一次经济升级免费获一村民」）</t>
         </is>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>匈奴</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>火药和僧侣文明</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -3702,19 +3588,19 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「不需要房屋，但初始木材-100」）</t>
+          <t>火药和僧侣文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「建筑工速度+30%」）</t>
         </is>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>亚美尼亚</t>
+          <t>西西里</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>步兵和海军文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -3724,19 +3610,19 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「骡车费用-25%」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「初始石料+100」）</t>
         </is>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>印度斯坦</t>
+          <t>匈奴</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>骆驼和火药文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -3746,19 +3632,19 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>骆驼和火药文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「村民黑暗/封建/城堡/帝王费用-8/13/18/23%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「不需要房屋，但初始木材-100」）</t>
         </is>
       </c>
     </row>
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>亚美尼亚</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>步弓手和火药文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -3768,34 +3654,78 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>步弓手和火药文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「初始村民+3，木材-50，食物-200」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「骡车费用-25%」）</t>
         </is>
       </c>
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>印度斯坦</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>骆驼和火药文明</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>无一条直接加强弓兵</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>骆驼和火药文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「村民黑暗/封建/城堡/帝王费用-8/13/18/23%」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>步弓手和火药文明</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>无一条直接加强弓兵</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>步弓手和火药文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「初始村民+3，木材-50，食物-200」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
           <t>雅典</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>步兵和海军文明</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>无一条直接加强弓兵</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>步兵和海军文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「TC可切换政策风格（经济/海军/军事）」）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D31"/>
+  <autoFilter ref="A1:D33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -4150,22 +4080,22 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>拜占庭</t>
+          <t>维京</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>骆驼/掷矛/长矛兵费用-25%</t>
+          <t>博格斯维加尔（弓兵系/维京长船攻+1）</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0）；弓兵科技树 13/14。缺：帝王掷矛手</t>
+          <t>原生条目 1 条（强 1）；弓兵科技树 12/14。缺：扳指、帝王掷矛手</t>
         </is>
       </c>
     </row>
@@ -4175,22 +4105,22 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>王家敕令骑兵（骑马弩手黄金-40%）</t>
+          <t>兵营/靶场/马厩可用招募训令</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；弓兵科技树 9/14。缺：强弩兵、扳指、护腕、帝王掷矛手、环甲</t>
+          <t>原生条目 1 条（强 0）；弓兵科技树 6/14。缺：强弩兵、弩手、弓兵、护腕、弹道学</t>
         </is>
       </c>
     </row>
@@ -4200,22 +4130,22 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>骑兵对掷矛手攻+2</t>
+          <t>步弓/意大利佣兵近战护甲+1/远程护甲+1</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；弓兵科技树 12/14。缺：扳指、帝王掷矛手</t>
+          <t>原生条目 1 条（强 0）；弓兵科技树 13/14。缺：帝王掷矛手</t>
         </is>
       </c>
     </row>
@@ -4275,7 +4205,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1">
+    <row r="2" ht="51" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -4284,7 +4214,7 @@
           <t>不列颠</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -4294,9 +4224,9 @@
           <t>免费位</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>步弓手城堡/帝王射程+1/+2；英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>步弓手城堡/帝王射程+1/+2；英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）；靶场工作速度 +10%</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -4314,7 +4244,7 @@
           <t>玛雅</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -4324,7 +4254,7 @@
           <t>免费位</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
         </is>
@@ -4344,7 +4274,7 @@
           <t>埃塞俄比亚</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -4354,7 +4284,7 @@
           <t>免费位</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>步弓手攻击速度+18%</t>
         </is>
@@ -4384,9 +4314,9 @@
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>弩箭匣（弓兵系/战车/楼船可发更多弩箭）；步弓手视野 +2；弓兵靶场/铁匠铺科技-25%</t>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>步弓手视野 +2；弩箭匣（弓兵系/战车/楼船可发更多弩箭）</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -4414,7 +4344,7 @@
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）；织物盾（印加枪兵长/投石手/蔷琵战士近战护甲+1/远程护甲+1）</t>
         </is>
@@ -4444,9 +4374,9 @@
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>Malon突袭（掷石绳骑兵/投石手/掷矛手可穿透伤害）；长矛兵系和掷矛手视野 +2；聚落可训长矛/掷矛</t>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Malon突袭（掷石绳骑兵/投石手/掷矛手可穿透伤害）；步兵/投石手/掷矛封建/城堡/帝王生命+5/10/15；长矛兵系和掷矛手视野 +2</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -4474,7 +4404,7 @@
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>蔷琵战士/靶场封建/城堡/帝王近战护甲+1/2/3；草药医学（弓兵系/蔷琵战士移速+15%）</t>
         </is>
@@ -4485,7 +4415,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="51" customHeight="1">
+    <row r="9" ht="36" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
@@ -4504,9 +4434,9 @@
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>卡西克（蔷琵战士/投石手攻速+25%）；箭毒（步弓手/防御工事造成中毒伤害）；靶场/兵营升级食物-50%</t>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>卡西克（蔷琵战士/投石手攻速+25%）；箭毒（步弓手/防御工事造成中毒伤害）</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -4534,7 +4464,7 @@
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>掷矛手/骑象弓兵攻速+25%</t>
         </is>
@@ -4564,7 +4494,7 @@
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>市政/古典掷矛手每分钟回5/10生命；轻装盾兵（掷矛手造成穿透伤害）</t>
         </is>
@@ -4596,7 +4526,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>在帝王时代可升级为帝王掷矛手；步弓/掷矛生命+20%</t>
+          <t>步弓/掷矛生命+20%；在帝王时代可升级为帝王掷矛手</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -4641,7 +4571,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>拜占庭</t>
+          <t>维京</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -4656,22 +4586,22 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>骆驼/掷矛/长矛兵费用-25%</t>
+          <t>博格斯维加尔（弓兵系/维京长船攻+1）</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 13/14；缺 帝王掷矛手</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 12/14；缺 扳指、帝王掷矛手；最直接一条：博格斯维加尔（弓兵系/维京长船攻+1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -4686,12 +4616,12 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>王家敕令骑兵（骑马弩手黄金-40%）</t>
+          <t>兵营/靶场/马厩可用招募训令</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 9/14；缺 强弩兵、扳指、护腕、帝王掷矛手；最直接一条：王家敕令骑兵（骑马弩手黄金-40%）</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；弓兵科技树 6/14；缺 强弩兵、弩手、弓兵、护腕</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4631,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -4716,12 +4646,12 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>骑兵对掷矛手攻+2</t>
+          <t>步弓/意大利佣兵近战护甲+1/远程护甲+1</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 12/14；缺 扳指、帝王掷矛手；最直接一条：骑兵对掷矛手攻+2</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 13/14；缺 帝王掷矛手</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4661,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>维京</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -4746,12 +4676,12 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>博格斯维加尔（弓兵系/维京长船攻+1）</t>
+          <t>步弓手和掷矛手对建筑的攻击力 +2</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 12/14；缺 扳指、帝王掷矛手；最直接一条：博格斯维加尔（弓兵系/维京长船攻+1）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：步弓手和掷矛手对建筑的攻击力 +2</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4691,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>马其顿人</t>
+          <t>契丹</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -4776,12 +4706,12 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>兵营/靶场/马厩可用招募训令</t>
+          <t>札甲（步兵/掷矛手反弹25%近战伤害）；掷矛/长矛/斥候骑兵系训练升级+15%</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；弓兵科技树 6/14；缺 强弩兵、弩手、弓兵、护腕</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；弓兵科技树 12/14；缺 强弩兵、帝王掷矛手；最直接一条：札甲（步兵/掷矛手反弹25%近战伤害）</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4721,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>阿兹特克</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -4806,12 +4736,12 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>步弓/意大利佣兵近战护甲+1/远程护甲+1</t>
+          <t>掷矛器（掷矛手攻+1，射程+1）</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 13/14；缺 帝王掷矛手</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 11/14；缺 扳指、帝王掷矛手、环甲；最直接一条：掷矛器（掷矛手攻+1，射程+1）</t>
         </is>
       </c>
     </row>
@@ -4821,7 +4751,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>瞿折罗</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -4836,12 +4766,12 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>骑射手对远程攻+2（掷矛手除外）</t>
+          <t>边防部队（骆驼/骑象弓兵近战护甲+4）</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：骑射手对远程攻+2（掷矛手除外）</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 11/14；缺 强弩兵、帝王掷矛手、环甲</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4781,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>阿契美尼德</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -4866,22 +4796,22 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>步弓手和掷矛手对建筑的攻击力 +2</t>
+          <t>芦苇箭（弓兵/远程长生军/箭船攻速+25%）</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 13/14；缺 帝王掷矛手；最直接一条：步弓手和掷矛手对建筑的攻击力 +2</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 9/14；缺 强弩兵、弹道学、帝王掷矛手、化学</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="51" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>契丹</t>
+          <t>普鲁人</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -4896,12 +4826,12 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>札甲（步兵/掷矛手反弹25%近战伤害）；掷矛/长矛/斥候骑兵系训练升级+15%</t>
+          <t>叶头箭杆（帕提尤达长弓兵提升近距伤害）</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；弓兵科技树 12/14；缺 强弩兵、帝王掷矛手；最直接一条：札甲（步兵/掷矛手反弹25%近战伤害）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 7/14；缺 强弩兵、弩手、弓兵、扳指；最直接一条：叶头箭杆（帕提尤达长弓兵提升近距伤害）</t>
         </is>
       </c>
     </row>
@@ -4911,7 +4841,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>阿兹特克</t>
+          <t>柏柏尔</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -4926,22 +4856,22 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>掷矛器（掷矛手攻+1，射程+1）</t>
+          <t>从城堡时代开始，靶场提供标枪骑兵</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 11/14；缺 扳指、帝王掷矛手、环甲；最直接一条：掷矛器（掷矛手攻+1，射程+1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；弓兵科技树 12/14；缺 强弩兵、帝王掷矛手</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>吴</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -4956,22 +4886,22 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>波斯步弓手（弓兵系消耗额外木材而非黄金）</t>
+          <t>赤壁战术（爆破船/火焰弓箭手对船只/建筑火焰伤害）</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 11/14；缺 强弩兵、护腕、帝王掷矛手；最直接一条：波斯步弓手（弓兵系消耗额外木材而非黄金）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；弓兵科技树 11/14；缺 扳指、帝王掷矛手、环甲</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>普鲁人</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -4986,12 +4916,12 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>叶头箭杆（帕提尤达长弓兵提升近距伤害）</t>
+          <t>希洛人征兵（长矛/掷矛/村民训练+50%）</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 7/14；缺 强弩兵、弩手、弓兵、扳指；最直接一条：叶头箭杆（帕提尤达长弓兵提升近距伤害）</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 9/14；缺 强弩兵、弹道学、帝王掷矛手、化学</t>
         </is>
       </c>
     </row>
@@ -5001,7 +4931,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>拜占庭</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -5016,22 +4946,22 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>从城堡时代开始，靶场提供标枪骑兵</t>
+          <t>骆驼/掷矛/长矛兵费用-25%</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；弓兵科技树 12/14；缺 强弩兵、帝王掷矛手</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="36" customHeight="1">
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 13/14；缺 帝王掷矛手</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="51" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>法兰克</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -5046,22 +4976,22 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>靶场/马厩木材-75</t>
+          <t>王家敕令骑兵（骑马弩手黄金-40%）</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；弓兵科技树 11/14；缺 强弩兵、护腕、帝王掷矛手</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="36" customHeight="1">
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 9/14；缺 强弩兵、扳指、护腕、帝王掷矛手；最直接一条：王家敕令骑兵（骑马弩手黄金-40%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="51" customHeight="1">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>吴</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -5076,12 +5006,12 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>赤壁战术（爆破船/火焰弓箭手对船只/建筑火焰伤害）</t>
+          <t>波斯步弓手（弓兵系消耗额外木材而非黄金）</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；弓兵科技树 11/14；缺 扳指、帝王掷矛手、环甲</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；弓兵科技树 11/14；缺 强弩兵、护腕、帝王掷矛手；最直接一条：波斯步弓手（弓兵系消耗额外木材而非黄金）</t>
         </is>
       </c>
     </row>
@@ -5091,7 +5021,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>瞿折罗</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
@@ -5106,12 +5036,12 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>边防部队（骆驼/骑象弓兵近战护甲+4）</t>
+          <t>靶场/马厩木材-75</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 11/14；缺 强弩兵、帝王掷矛手、环甲</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 0）；弓兵科技树 11/14；缺 强弩兵、护腕、帝王掷矛手</t>
         </is>
       </c>
     </row>
@@ -5121,7 +5051,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>阿契美尼德</t>
+          <t>高丽</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
@@ -5136,12 +5066,12 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>芦苇箭（弓兵/远程长生军/箭船攻速+25%）</t>
+          <t>弓兵护甲/塔升级免费（升级炮塔需要化学）</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 9/14；缺 强弩兵、弹道学、帝王掷矛手、化学</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 13/14；缺 帝王掷矛手</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5081,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>斯巴达</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
@@ -5166,12 +5096,12 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>希洛人征兵（长矛/掷矛/村民训练+50%）</t>
+          <t>所有单位黄金费用-20%</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 9/14；缺 强弩兵、弹道学、帝王掷矛手、化学</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 13/14；缺 帝王掷矛手</t>
         </is>
       </c>
     </row>
@@ -5181,27 +5111,27 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
+          <t>保加利亚</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2000 金</t>
+          <t>不建议</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>弓兵护甲/塔升级免费（升级炮塔需要化学）</t>
+          <t>无一条直接加强弓兵</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 13/14；缺 帝王掷矛手</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「民兵系升级免费」）</t>
         </is>
       </c>
     </row>
@@ -5211,27 +5141,27 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
+          <t>波兰</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2000 金</t>
+          <t>不建议</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>所有单位黄金费用-20%</t>
+          <t>无一条直接加强弓兵</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；弓兵科技树 13/14；缺 帝王掷矛手</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「大庄园替代磨坊」）</t>
         </is>
       </c>
     </row>
@@ -5241,10 +5171,10 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>保加利亚</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
+          <t>波希米亚</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5261,7 +5191,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「民兵系升级免费」）</t>
+          <t>火药和僧侣文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「采矿场科技免费」）</t>
         </is>
       </c>
     </row>
@@ -5271,10 +5201,10 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>波兰</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="inlineStr">
+          <t>勃艮第</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5291,7 +5221,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「大庄园替代磨坊」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「可提前一个时代经济升级且食物-40%」）</t>
         </is>
       </c>
     </row>
@@ -5301,10 +5231,10 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>波希米亚</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
+          <t>鞑靼</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5321,7 +5251,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>火药和僧侣文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「采矿场科技免费」）</t>
+          <t>骑射手文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「牲畜持续时间+50%」）</t>
         </is>
       </c>
     </row>
@@ -5331,10 +5261,10 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>勃艮第</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="inlineStr">
+          <t>丹麦人</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5351,7 +5281,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「可提前一个时代经济升级且食物-40%」）</t>
+          <t>步兵和攻城文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「捕鱼船/村民存食+5%」）</t>
         </is>
       </c>
     </row>
@@ -5361,10 +5291,10 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>鞑靼</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="inlineStr">
+          <t>高棉</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5381,7 +5311,7 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>骑射手文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「牲畜持续时间+50%」）</t>
+          <t>攻城武器和大象文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「无需建筑即可升时代/解锁建筑」）</t>
         </is>
       </c>
     </row>
@@ -5391,10 +5321,10 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>丹麦人</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="inlineStr">
+          <t>哥特</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5411,7 +5341,7 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「捕鱼船/村民存食+5%」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「可立即研究织布机」）</t>
         </is>
       </c>
     </row>
@@ -5421,10 +5351,10 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>高棉</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
+          <t>格鲁吉亚</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5441,7 +5371,7 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>攻城武器和大象文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「无需建筑即可升时代/解锁建筑」）</t>
+          <t>防御和骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「开局有骡车」）</t>
         </is>
       </c>
     </row>
@@ -5451,10 +5381,10 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>哥特</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
+          <t>凯尔特</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5471,7 +5401,7 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「可立即研究织布机」）</t>
+          <t>步兵和攻城武器文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「伐木工速度+15%」）</t>
         </is>
       </c>
     </row>
@@ -5481,10 +5411,10 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>格鲁吉亚</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
+          <t>罗马</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5501,7 +5431,7 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>防御和骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「开局有骡车」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「村民收集/建造/修理速度+5%」）</t>
         </is>
       </c>
     </row>
@@ -5511,10 +5441,10 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>凯尔特</t>
-        </is>
-      </c>
-      <c r="C43" s="8" t="inlineStr">
+          <t>马来</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5531,7 +5461,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城武器文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「伐木工速度+15%」）</t>
+          <t>海军文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「升时代速度+66%」）</t>
         </is>
       </c>
     </row>
@@ -5541,10 +5471,10 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
-        </is>
-      </c>
-      <c r="C44" s="8" t="inlineStr">
+          <t>马里</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5561,7 +5491,7 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「村民收集/建造/修理速度+5%」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「建筑木材-15%」）</t>
         </is>
       </c>
     </row>
@@ -5571,10 +5501,10 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
-        </is>
-      </c>
-      <c r="C45" s="8" t="inlineStr">
+          <t>马扎尔</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5591,7 +5521,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>海军文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「升时代速度+66%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「村民一击杀狼」）</t>
         </is>
       </c>
     </row>
@@ -5601,10 +5531,10 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>马里</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="inlineStr">
+          <t>蒙古</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5621,7 +5551,7 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「建筑木材-15%」）</t>
+          <t>骑射手文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「猎人速度+40%」）</t>
         </is>
       </c>
     </row>
@@ -5631,10 +5561,10 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>马扎尔</t>
-        </is>
-      </c>
-      <c r="C47" s="8" t="inlineStr">
+          <t>孟加拉</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5651,7 +5581,7 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「村民一击杀狼」）</t>
+          <t>象兵和海军文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「升时代TC产生2村民」）</t>
         </is>
       </c>
     </row>
@@ -5661,10 +5591,10 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>蒙古</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="inlineStr">
+          <t>缅甸</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5681,7 +5611,7 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>骑射手文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「猎人速度+40%」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「伐木场科技免费」）</t>
         </is>
       </c>
     </row>
@@ -5691,10 +5621,10 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>缅甸</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="inlineStr">
+          <t>女真</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5711,7 +5641,7 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「伐木场科技免费」）</t>
+          <t>骑兵和火药文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
         </is>
       </c>
     </row>
@@ -5721,10 +5651,10 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>女真</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="inlineStr">
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5741,7 +5671,7 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>骑兵和火药文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于弓兵。（它最强的一条功能是「磨坊/伐木场/采矿场费用-50%」）</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5684,7 @@
           <t>撒克逊人</t>
         </is>
       </c>
-      <c r="C51" s="8" t="inlineStr">
+      <c r="C51" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5784,7 +5714,7 @@
           <t>斯拉夫</t>
         </is>
       </c>
-      <c r="C52" s="8" t="inlineStr">
+      <c r="C52" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5814,7 +5744,7 @@
           <t>条顿</t>
         </is>
       </c>
-      <c r="C53" s="8" t="inlineStr">
+      <c r="C53" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5844,7 +5774,7 @@
           <t>土耳其</t>
         </is>
       </c>
-      <c r="C54" s="8" t="inlineStr">
+      <c r="C54" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5874,7 +5804,7 @@
           <t>瓦兰吉人</t>
         </is>
       </c>
-      <c r="C55" s="8" t="inlineStr">
+      <c r="C55" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5904,7 +5834,7 @@
           <t>魏</t>
         </is>
       </c>
-      <c r="C56" s="8" t="inlineStr">
+      <c r="C56" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5934,7 +5864,7 @@
           <t>西班牙</t>
         </is>
       </c>
-      <c r="C57" s="8" t="inlineStr">
+      <c r="C57" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5964,7 +5894,7 @@
           <t>西西里</t>
         </is>
       </c>
-      <c r="C58" s="8" t="inlineStr">
+      <c r="C58" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5994,7 +5924,7 @@
           <t>匈奴</t>
         </is>
       </c>
-      <c r="C59" s="8" t="inlineStr">
+      <c r="C59" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -6024,7 +5954,7 @@
           <t>亚美尼亚</t>
         </is>
       </c>
-      <c r="C60" s="8" t="inlineStr">
+      <c r="C60" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -6054,7 +5984,7 @@
           <t>印度斯坦</t>
         </is>
       </c>
-      <c r="C61" s="8" t="inlineStr">
+      <c r="C61" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -6084,7 +6014,7 @@
           <t>中国</t>
         </is>
       </c>
-      <c r="C62" s="8" t="inlineStr">
+      <c r="C62" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -6114,7 +6044,7 @@
           <t>雅典</t>
         </is>
       </c>
-      <c r="C63" s="8" t="inlineStr">
+      <c r="C63" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
